--- a/JsonConverter/ExcelFiles/OO_Codex.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Codex.xlsx
@@ -86,7 +86,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -142,6 +142,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -202,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -244,6 +259,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,42 +550,42 @@
   <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="22" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
-    <col width="24" customWidth="1" style="3" min="3" max="3"/>
-    <col width="72" customWidth="1" style="3" min="4" max="4"/>
-    <col width="30" customWidth="1" style="3" min="5" max="5"/>
-    <col width="28" customWidth="1" style="3" min="6" max="6"/>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="15" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="6" max="6"/>
     <col width="12.54296875" customWidth="1" style="3" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>도감 고유 ID</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>도감 분류</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>도감 제목</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>도감 설명</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>도감 이미지 경로</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>해금 조건</t>
         </is>
@@ -577,32 +601,32 @@
       <c r="O1" s="18" t="n"/>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -618,32 +642,32 @@
       <c r="O2" s="18" t="n"/>
     </row>
     <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>ImagePath</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>UnlockCondition</t>
         </is>
@@ -679,7 +703,7 @@
           <t>춘향이 건넨 첫 여정의 재료. 모란의 요리마차에서 따뜻한 밥으로 다시 태어날 수 있다.</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr"/>
+      <c r="E4" s="21" t="n"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t>StartRoad_FirstInventory</t>

--- a/JsonConverter/ExcelFiles/OO_Codex.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Codex.xlsx
@@ -685,28 +685,28 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>OO_Codex_1</t>
+          <t>OO_Codex_Character_Moran</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Ingredient</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>쌀</t>
+          <t>모란</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>춘향이 건넨 첫 여정의 재료. 모란의 요리마차에서 따뜻한 밥으로 다시 태어날 수 있다.</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="n"/>
+          <t>모란은 푸드카리지를 이끌고 길을 떠나는 주인공입니다. 각 지역에서 재료를 모으고 요리를 완성하며, 굶주린 사람들과 동물들의 문제를 해결해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>StartRoad_FirstInventory</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="G4" s="18" t="n"/>
@@ -720,12 +720,32 @@
       <c r="O4" s="18" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>OO_Codex_Character_Chunyang</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>춘양</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>춘양은 초반 여정에서 모란을 돕는 화자이자 동료입니다. 부드럽고 따뜻한 말투로 상황을 설명하며, 플레이어가 첫 임무와 세계관을 자연스럽게 이해하도록 도와줍니다.</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr"/>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
       <c r="G5" s="18" t="n"/>
       <c r="H5" s="18" t="n"/>
       <c r="I5" s="18" t="n"/>
@@ -737,12 +757,32 @@
       <c r="O5" s="18" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="18" t="n"/>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>OO_Codex_Character_Rabbit</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>토끼</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>토끼는 Stage4_2에서 멀리서 놀리듯 등장하는 장난기 많은 캐릭터입니다. 당근전을 좋아하며, 모란은 요리를 이용해 토끼를 유혹하고 잠들게 해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr"/>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Stage4</t>
+        </is>
+      </c>
       <c r="G6" s="18" t="n"/>
       <c r="H6" s="18" t="n"/>
       <c r="I6" s="18" t="n"/>
@@ -754,12 +794,36 @@
       <c r="O6" s="18" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>OO_Codex_Food_KoreanCake</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>떡</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>절구에 쌀을 찧어 만든 쫄깃한 떡입니다. 꿀과 조합하면 꿀떡이 되고, 당근과 조합하면 당근전분이 되므로 Stage3 이후 핵심 재료로 계속 쓰입니다.</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Images/Food/KoreanCake</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Stage3</t>
+        </is>
+      </c>
       <c r="G7" s="18" t="n"/>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="n"/>
@@ -771,12 +835,36 @@
       <c r="O7" s="18" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>OO_Codex_Food_CarrotCake</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>당근전</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>당근전분을 가마솥에 익혀 만든 고소한 당근전입니다. 토끼를 유혹하고 잠들게 하는 Stage4 핵심 음식이며, 마지막 임무 진행에 반드시 필요합니다.</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Images/Food/CarrotCake</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Stage4</t>
+        </is>
+      </c>
       <c r="G8" s="18" t="n"/>
       <c r="H8" s="18" t="n"/>
       <c r="I8" s="18" t="n"/>
@@ -788,12 +876,36 @@
       <c r="O8" s="18" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>OO_Codex_Stage_4</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>북쪽 토끼와 거북이</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>북쪽 농경지대는 토끼와 거북이의 마지막 의뢰가 펼쳐지는 장소입니다. 모란은 당근전을 만들어 토끼를 유혹하고, 모든 스테이지 임무를 마무리합니다.</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Images/Stages/Stage4_1Background</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Stage4</t>
+        </is>
+      </c>
       <c r="G9" s="18" t="n"/>
       <c r="H9" s="18" t="n"/>
       <c r="I9" s="18" t="n"/>
